--- a/file/04.2026v2.xlsx
+++ b/file/04.2026v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\demon\Documents\Best Teller 01\Best teller bata\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B9F6BF-0AFE-4CB7-8F6A-9B5C655DF4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F339F2A0-1292-4650-89EA-AF3E07D1C220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="824" firstSheet="10" activeTab="24" xr2:uid="{D6DDC371-C281-4E5D-B6C2-4CADD0F1436D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="824" xr2:uid="{D6DDC371-C281-4E5D-B6C2-4CADD0F1436D}"/>
   </bookViews>
   <sheets>
     <sheet name="Rank_Teller" sheetId="149" r:id="rId1"/>
@@ -3684,13 +3684,13 @@
     <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3699,20 +3699,20 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="26">
@@ -5378,7 +5378,7 @@
     <col min="6" max="6" width="13.42578125" style="2" customWidth="1"/>
     <col min="7" max="7" width="26.28515625" style="2" customWidth="1"/>
     <col min="8" max="8" width="24.42578125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.42578125" style="2" customWidth="1"/>
     <col min="11" max="11" width="13.140625" style="1" customWidth="1"/>
     <col min="12" max="12" width="11.42578125" style="5" customWidth="1"/>
@@ -5399,19 +5399,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -5422,38 +5422,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -5468,10 +5468,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -5504,11 +5504,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -30469,7 +30469,7 @@
       <c r="B377" s="30"/>
       <c r="E377" s="32"/>
       <c r="F377" s="23"/>
-      <c r="I377" s="41"/>
+      <c r="I377" s="18"/>
       <c r="J377" s="18"/>
       <c r="K377" s="44"/>
       <c r="L377" s="39"/>
@@ -30791,19 +30791,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -30814,38 +30814,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -30860,10 +30860,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -30896,11 +30896,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -31576,19 +31576,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -31599,38 +31599,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -31645,10 +31645,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -31681,11 +31681,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -32495,19 +32495,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -32518,38 +32518,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -32564,10 +32564,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -32600,11 +32600,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -33146,19 +33146,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -33169,38 +33169,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -33215,10 +33215,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -33251,11 +33251,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -36343,19 +36343,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -36366,38 +36366,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -36412,10 +36412,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -36448,11 +36448,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -37262,19 +37262,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -37285,38 +37285,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -37331,10 +37331,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -37367,11 +37367,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -38450,19 +38450,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -38473,38 +38473,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -38519,10 +38519,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -38555,11 +38555,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -39637,19 +39637,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -39660,38 +39660,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -39706,10 +39706,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -39742,11 +39742,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -40489,19 +40489,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -40512,38 +40512,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -40558,10 +40558,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -40594,11 +40594,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -41542,19 +41542,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -41565,38 +41565,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -41611,10 +41611,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -41647,11 +41647,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -44538,19 +44538,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -44561,38 +44561,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -44607,10 +44607,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -44643,11 +44643,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -56445,19 +56445,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -56468,38 +56468,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -56514,10 +56514,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -56550,11 +56550,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -57431,19 +57431,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -57454,38 +57454,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -57500,10 +57500,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -57536,11 +57536,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -58350,19 +58350,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -58373,38 +58373,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -58419,10 +58419,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -58455,11 +58455,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -59135,19 +59135,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -59158,38 +59158,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -59204,10 +59204,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -59240,11 +59240,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -59920,19 +59920,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -59943,38 +59943,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -59989,10 +59989,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -60025,11 +60025,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -60639,19 +60639,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -60662,38 +60662,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -60708,10 +60708,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -60744,11 +60744,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -63367,19 +63367,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -63390,38 +63390,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -63436,10 +63436,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -63472,11 +63472,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -77151,19 +77151,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -77174,38 +77174,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -77220,10 +77220,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -77256,11 +77256,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -81286,19 +81286,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -81309,38 +81309,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -81355,10 +81355,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -81391,11 +81391,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -82607,19 +82607,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -82630,38 +82630,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -82676,10 +82676,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -82712,11 +82712,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -84331,19 +84331,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -84354,38 +84354,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -84400,10 +84400,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -84436,11 +84436,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -86456,19 +86456,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -86479,38 +86479,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -86525,10 +86525,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -86561,11 +86561,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
@@ -87911,19 +87911,19 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="19"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="96"/>
+      <c r="C1" s="95"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="96" t="s">
         <v>637</v>
       </c>
-      <c r="J1" s="103"/>
+      <c r="J1" s="96"/>
       <c r="K1" s="97" t="s">
         <v>908</v>
       </c>
@@ -87934,38 +87934,38 @@
       </c>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="99" t="s">
         <v>631</v>
       </c>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
       <c r="U1" s="71" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="54" x14ac:dyDescent="0.4">
       <c r="A2" s="19"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="100" t="s">
         <v>383</v>
       </c>
       <c r="J2" s="101" t="s">
         <v>486</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="L2" s="100" t="s">
+      <c r="L2" s="103" t="s">
         <v>385</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="102" t="s">
         <v>386</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -87980,10 +87980,10 @@
       <c r="Q2" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="S2" s="95"/>
+      <c r="S2" s="94"/>
       <c r="T2" s="35" t="s">
         <v>635</v>
       </c>
@@ -88016,11 +88016,11 @@
       <c r="H3" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="101"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="99"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="102"/>
       <c r="N3" s="14">
         <v>70</v>
       </c>
